--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484026_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484026_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1493</v>
+        <v>2.1829</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4133</v>
+        <v>2.4691</v>
       </c>
       <c r="F2" t="n">
-        <v>0.736</v>
+        <v>-0.2862</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.0301</v>
+        <v>0.9227</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.4913</v>
+        <v>1.8489</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4613</v>
+        <v>-0.9263</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1201</v>
+        <v>1.1492</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1603</v>
+        <v>1.1492</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.91</v>
+        <v>-0.2265</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3311</v>
+        <v>0.6997</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4211</v>
+        <v>-0.9263</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="S2" t="n">
-        <v>2.247</v>
+        <v>-0.343</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4658</v>
+        <v>0.1134</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2188</v>
+        <v>-0.4564</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9405</v>
+        <v>1.2065</v>
       </c>
       <c r="W2" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4431</v>
+        <v>1.9283</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6731</v>
+        <v>0.9679</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.23</v>
+        <v>0.9605</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9227</v>
+        <v>-1.0301</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8489</v>
+        <v>-1.4913</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9263</v>
+        <v>0.4613</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1492</v>
+        <v>-0.1201</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1492</v>
+        <v>-0.1603</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2265</v>
+        <v>-0.91</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6997</v>
+        <v>-1.3311</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9263</v>
+        <v>0.4211</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0828</v>
+        <v>1.026</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3175</v>
+        <v>1.0204</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4003</v>
+        <v>0.0056</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2065</v>
+        <v>0.9405</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4261</v>
+        <v>0.8863</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5834</v>
+        <v>-0.0109</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0094</v>
+        <v>0.8972</v>
       </c>
       <c r="G4" t="n">
         <v>-0.457</v>
@@ -766,13 +766,13 @@
         <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3072</v>
+        <v>0.153</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3117</v>
+        <v>0.2608</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0045</v>
+        <v>-0.1077</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>O. BAJJA SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6408</v>
+        <v>-0.6787</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1775</v>
+        <v>-0.6614</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8183</v>
+        <v>-0.0173</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6716</v>
+        <v>-1.2119</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3634</v>
+        <v>-0.857</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6918</v>
+        <v>-0.355</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2407</v>
+        <v>0.1208</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2783</v>
+        <v>0.0806</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0376</v>
+        <v>0.0402</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-1.3327</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0851</v>
+        <v>-0.9376</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6542</v>
+        <v>-0.3951</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4812</v>
+        <v>-0.1927</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1191</v>
+        <v>-0.1077</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3621</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. BAJJA SANCHEZ</t>
+          <t>A. CORTEGANO NAVARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0573</v>
+        <v>-0.8133</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9278</v>
+        <v>-0.3506</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1295</v>
+        <v>-0.4627</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2119</v>
+        <v>-0.8033</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.857</v>
+        <v>1.3408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.355</v>
+        <v>-2.1441</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1208</v>
+        <v>0.4806</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0806</v>
+        <v>1.841</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0402</v>
+        <v>-1.3604</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3327</v>
+        <v>-1.2839</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9376</v>
+        <v>-0.5002</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3951</v>
+        <v>-0.7837</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.9596</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5713</v>
+        <v>-0.2452</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3741</v>
+        <v>0.3855</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1973</v>
+        <v>-0.6307</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.266</v>
+        <v>3.2109</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6745</v>
+        <v>3.7428</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4085</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5743</v>
+        <v>-0.8769</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4391</v>
+        <v>0.1378</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1351</v>
+        <v>-1.0147</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4956</v>
+        <v>1.6716</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9423</v>
+        <v>2.3634</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5533</v>
+        <v>-0.6918</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0692</v>
+        <v>2.2407</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5709</v>
+        <v>2.2783</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.64</v>
+        <v>-0.0376</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4264</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5132</v>
+        <v>0.0851</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9133</v>
+        <v>-0.6542</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7935</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9758</v>
+        <v>-2.1822</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1822</v>
+        <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8457</v>
+        <v>0.2451</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.0794</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0217</v>
+        <v>0.1657</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8692</v>
+        <v>-1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8692</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5997</v>
+        <v>-1.5053</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6659</v>
+        <v>-2.7679</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0662</v>
+        <v>1.2626</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0343</v>
@@ -1078,13 +1078,13 @@
         <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>0.165</v>
+        <v>0.2593</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3061</v>
+        <v>0.2041</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1412</v>
+        <v>0.0552</v>
       </c>
       <c r="V8" t="n">
         <v>0.0713</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CORTEGANO NAVARRO</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.369</v>
+        <v>-2.1422</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5976</v>
+        <v>-0.5582</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7714</v>
+        <v>-1.584</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8033</v>
+        <v>-2.4956</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3408</v>
+        <v>-0.9423</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1441</v>
+        <v>-1.5533</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4806</v>
+        <v>-0.0692</v>
       </c>
       <c r="K9" t="n">
-        <v>1.841</v>
+        <v>0.5709</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3604</v>
+        <v>-0.64</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2839</v>
+        <v>-2.4264</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5002</v>
+        <v>-1.5132</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7837</v>
+        <v>-0.9133</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.7935</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-2.9758</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-4.9596</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8008</v>
+        <v>0.2777</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8615</v>
+        <v>0.7483</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9393</v>
+        <v>-0.4706</v>
       </c>
       <c r="V9" t="n">
-        <v>3.2109</v>
+        <v>0.8692</v>
       </c>
       <c r="W9" t="n">
-        <v>3.7428</v>
+        <v>1.7384</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.532</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7578</v>
+        <v>-2.193</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1463</v>
+        <v>-0.7778</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6115</v>
+        <v>-1.4151</v>
       </c>
       <c r="G10" t="n">
         <v>0.2903</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.048</v>
+        <v>-0.4832</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5611</v>
+        <v>-0.1927</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4869</v>
+        <v>-0.2905</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2065</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3998</v>
+        <v>-3.9064</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4728</v>
+        <v>-2.9488</v>
       </c>
       <c r="F11" t="n">
-        <v>0.073</v>
+        <v>-0.9575</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.6176</v>
+        <v>0.4781</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0707</v>
+        <v>1.9551</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6883</v>
+        <v>-1.4769</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4778</v>
+        <v>0.0212</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4372</v>
+        <v>1.3816</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0406</v>
+        <v>-1.3604</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1398</v>
+        <v>0.4569</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5079</v>
+        <v>0.5735</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.1165</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1822</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.1741</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>0.666</v>
+        <v>-0.5314</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1791</v>
+        <v>0.2041</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5131</v>
+        <v>-0.7356</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7631</v>
+        <v>-5.0899</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8897</v>
+        <v>-5.0227</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8734</v>
+        <v>-0.0673</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4781</v>
+        <v>-2.6176</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9551</v>
+        <v>0.0707</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4769</v>
+        <v>-2.6883</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0212</v>
+        <v>-2.4778</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3816</v>
+        <v>-0.4372</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3604</v>
+        <v>-2.0406</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4569</v>
+        <v>-0.1398</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5735</v>
+        <v>0.5079</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1165</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3806</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q12" t="n">
         <v>-3.1741</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3882</v>
+        <v>-0.0241</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7368</v>
+        <v>0.6293</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6514</v>
+        <v>-0.6534</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="13">
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.1433</v>
+        <v>-12.2082</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.4587</v>
+        <v>-9.5235</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6846</v>
+        <v>-2.6845</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.2871</v>
+        <v>-7.287099999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>4.761399999999999</v>
+        <v>4.761400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-12.0485</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3012999999999993</v>
+        <v>-0.3013000000000003</v>
       </c>
       <c r="K13" t="n">
         <v>7.2134</v>
@@ -1450,16 +1450,16 @@
         <v>-7.5146</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.9859</v>
+        <v>-6.985900000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-2.4522</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.533800000000001</v>
+        <v>-4.533799999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.9434</v>
+        <v>-6.943399999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.8464</v>
@@ -1468,22 +1468,22 @@
         <v>11.903</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7934000000000004</v>
+        <v>0.1414999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4098</v>
+        <v>3.3449</v>
       </c>
       <c r="U13" t="n">
         <v>-3.2034</v>
       </c>
       <c r="V13" t="n">
-        <v>1.881</v>
+        <v>1.881000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>6.279199999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.398299999999999</v>
+        <v>-4.3983</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6149</v>
+        <v>7.7892</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9637</v>
+        <v>6.8617</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6512</v>
+        <v>0.9275</v>
       </c>
       <c r="G14" t="n">
         <v>4.2678</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7681</v>
+        <v>0.9424</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1168</v>
+        <v>1.0147</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3486</v>
+        <v>-0.0723</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5816</v>
+        <v>5.7832</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5914</v>
+        <v>4.294</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9903</v>
+        <v>1.4892</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4884</v>
+        <v>4.4803</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1155</v>
+        <v>1.8141</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6039</v>
+        <v>2.6662</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2082</v>
+        <v>4.1134</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8828</v>
+        <v>2.2634</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3253</v>
+        <v>1.85</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7197</v>
+        <v>0.367</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9983</v>
+        <v>-0.4493</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2786</v>
+        <v>0.8162</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3968</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
         <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9742</v>
+        <v>-0.4988</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8512</v>
+        <v>-0.0339</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1229</v>
+        <v>-0.4649</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0713</v>
+        <v>1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0713</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9567</v>
+        <v>3.8191</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5798</v>
+        <v>2.8569</v>
       </c>
       <c r="F16" t="n">
-        <v>1.377</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4803</v>
+        <v>1.4884</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8141</v>
+        <v>-0.1155</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6662</v>
+        <v>1.6039</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1134</v>
+        <v>2.2082</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2634</v>
+        <v>0.8828</v>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>1.3253</v>
       </c>
       <c r="M16" t="n">
-        <v>0.367</v>
+        <v>-0.7197</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4493</v>
+        <v>-0.9983</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8162</v>
+        <v>0.2786</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="R16" t="n">
         <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3252</v>
+        <v>1.2116</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7481</v>
+        <v>1.1167</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5770999999999999</v>
+        <v>0.0949</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3065</v>
+        <v>3.7759</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9968</v>
+        <v>2.915</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3098</v>
+        <v>0.8609</v>
       </c>
       <c r="G17" t="n">
         <v>0.4836</v>
@@ -1780,13 +1780,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3673</v>
+        <v>0.102</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7991</v>
+        <v>0.1191</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4318</v>
+        <v>-0.0171</v>
       </c>
       <c r="V17" t="n">
         <v>1.2065</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4281</v>
+        <v>2.1023</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2449</v>
+        <v>0.7551</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1832</v>
+        <v>1.3472</v>
       </c>
       <c r="G18" t="n">
         <v>1.7438</v>
@@ -1858,13 +1858,13 @@
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1093</v>
+        <v>-0.435</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.1133</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4858</v>
+        <v>-0.3217</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1877,11 +1877,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>,. VICENTE SABARIEGO</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1891,73 +1887,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0432</v>
+        <v>1.0128</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4364</v>
+        <v>-0.15</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6069</v>
+        <v>1.1628</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3062</v>
+        <v>0.429</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5111</v>
+        <v>-0.4741</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2048</v>
+        <v>0.9031</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3062</v>
+        <v>0.2013</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5111</v>
+        <v>0.121</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2048</v>
+        <v>0.0803</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.2277</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.5951</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.8227</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.3968</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2738</v>
+        <v>-0.0113</v>
       </c>
       <c r="T19" t="n">
-        <v>3.401</v>
+        <v>0.0454</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8728</v>
+        <v>-0.0567</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LARA</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1965,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8944</v>
+        <v>1.0128</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4471</v>
+        <v>-0.15</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3415</v>
+        <v>1.1628</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5254</v>
+        <v>0.429</v>
       </c>
       <c r="H20" t="n">
-        <v>1.159</v>
+        <v>-0.4741</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6335</v>
+        <v>0.9031</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0447</v>
+        <v>0.2013</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2755</v>
+        <v>0.121</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3202</v>
+        <v>0.0803</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5702</v>
+        <v>0.2277</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1165</v>
+        <v>-0.5951</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6867</v>
+        <v>0.8227</v>
       </c>
       <c r="P20" t="n">
         <v>0.5952</v>
@@ -2014,13 +2010,13 @@
         <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2262</v>
+        <v>-0.0113</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0056</v>
+        <v>0.0454</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2206</v>
+        <v>-0.0567</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2043,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7741</v>
+        <v>0.9603</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.861</v>
+        <v>-0.759</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6351</v>
+        <v>1.7193</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4205</v>
@@ -2092,13 +2088,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.3415</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6858</v>
+        <v>-0.5838</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1581</v>
+        <v>0.2423</v>
       </c>
       <c r="V21" t="n">
         <v>0.532</v>
@@ -2125,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2661</v>
+        <v>0.6385</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0554</v>
+        <v>2.2594</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7892</v>
+        <v>-1.6209</v>
       </c>
       <c r="G22" t="n">
         <v>3.734</v>
@@ -2170,13 +2166,13 @@
         <v>2.1822</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3128</v>
+        <v>0.0595</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0567</v>
+        <v>0.2608</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3696</v>
+        <v>-0.2013</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3534</v>
@@ -2189,7 +2185,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A. RODRIGUEZ LARA</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -2199,40 +2199,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3782</v>
+        <v>0.6062</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0683</v>
+        <v>-0.6512</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6901</v>
+        <v>1.2574</v>
       </c>
       <c r="G23" t="n">
-        <v>0.429</v>
+        <v>0.5254</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4741</v>
+        <v>1.159</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9031</v>
+        <v>-0.6335</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2013</v>
+        <v>-0.0447</v>
       </c>
       <c r="K23" t="n">
-        <v>0.121</v>
+        <v>1.2755</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0803</v>
+        <v>-1.3202</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2277</v>
+        <v>0.5702</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5951</v>
+        <v>-0.1165</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8227</v>
+        <v>0.6867</v>
       </c>
       <c r="P23" t="n">
         <v>0.5952</v>
@@ -2244,13 +2244,13 @@
         <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4023</v>
+        <v>-0.5144</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8728</v>
+        <v>-0.2097</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5294</v>
+        <v>-0.3048</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2265,7 +2265,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,67 +2277,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3782</v>
+        <v>-1.3714</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0683</v>
+        <v>-1.6042</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6901</v>
+        <v>0.2328</v>
       </c>
       <c r="G24" t="n">
-        <v>0.429</v>
+        <v>-0.3062</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4741</v>
+        <v>-1.5111</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9031</v>
+        <v>1.2048</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2013</v>
+        <v>-0.3062</v>
       </c>
       <c r="K24" t="n">
-        <v>0.121</v>
+        <v>-1.5111</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0803</v>
+        <v>1.2048</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2277</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5951</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8227</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5952</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.3968</v>
+        <v>-1.9838</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4023</v>
+        <v>1.8592</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8728</v>
+        <v>1.3604</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5294</v>
+        <v>0.4988</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="25">
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.165</v>
+        <v>-2.705</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.8908</v>
+        <v>-6.4827</v>
       </c>
       <c r="F25" t="n">
-        <v>3.7258</v>
+        <v>3.7777</v>
       </c>
       <c r="G25" t="n">
         <v>-3.6214</v>
@@ -2400,13 +2400,13 @@
         <v>2.3806</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8213</v>
+        <v>-0.3614</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3683</v>
+        <v>0.0398</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.453</v>
+        <v>-0.4012</v>
       </c>
       <c r="V25" t="n">
         <v>1.2777</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.0503</v>
+        <v>-3.7519</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.1757</v>
+        <v>-4.0736</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1253</v>
+        <v>0.3217</v>
       </c>
       <c r="G26" t="n">
         <v>-2.357</v>
@@ -2478,13 +2478,13 @@
         <v>0.9919</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0289</v>
+        <v>0.3273</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2438</v>
+        <v>0.3458</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2148</v>
+        <v>-0.0185</v>
       </c>
       <c r="V26" t="n">
         <v>-0.532</v>
@@ -2511,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.129</v>
+        <v>-4.1384</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.7408</v>
+        <v>-3.0266</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3882</v>
+        <v>-1.1119</v>
       </c>
       <c r="G27" t="n">
         <v>-3.1601</v>
@@ -2556,13 +2556,13 @@
         <v>0.5952</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.1591</v>
+        <v>-0.1686</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3627</v>
+        <v>0.3515</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.7964</v>
+        <v>-0.5201</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2065</v>
@@ -2589,19 +2589,19 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>12.7649</v>
+        <v>15.5336</v>
       </c>
       <c r="E28" t="n">
-        <v>1.616399999999998</v>
+        <v>3.0448</v>
       </c>
       <c r="F28" t="n">
-        <v>11.1489</v>
+        <v>12.4887</v>
       </c>
       <c r="G28" t="n">
-        <v>7.716099999999997</v>
+        <v>7.716100000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.2354</v>
+        <v>-5.235399999999999</v>
       </c>
       <c r="I28" t="n">
         <v>12.9517</v>
@@ -2610,7 +2610,7 @@
         <v>7.1873</v>
       </c>
       <c r="K28" t="n">
-        <v>2.572900000000001</v>
+        <v>2.572899999999999</v>
       </c>
       <c r="L28" t="n">
         <v>4.614100000000002</v>
@@ -2619,7 +2619,7 @@
         <v>0.5288999999999998</v>
       </c>
       <c r="N28" t="n">
-        <v>-7.8086</v>
+        <v>-7.808600000000001</v>
       </c>
       <c r="O28" t="n">
         <v>8.337300000000001</v>
@@ -2634,13 +2634,13 @@
         <v>19.8384</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.6085000000000007</v>
+        <v>2.1597</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3308</v>
+        <v>3.7589</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.9391</v>
+        <v>-1.5993</v>
       </c>
       <c r="V28" t="n">
         <v>-1.881</v>
